--- a/xls/square_12_tri3_24.xlsx
+++ b/xls/square_12_tri3_24.xlsx
@@ -482,13 +482,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.0009889748603231965</v>
+        <v>-0.0009889748459457365</v>
       </c>
       <c r="J24">
-        <v>-0.0005913365930059761</v>
+        <v>-0.000591336584607648</v>
       </c>
       <c r="K24">
-        <v>2.4728400781400377</v>
+        <v>2.4728400732764344</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.0003435023604634523</v>
+        <v>-0.0003435023603400655</v>
       </c>
       <c r="J25">
-        <v>-0.00024869615352739747</v>
+        <v>-0.00024869615344403186</v>
       </c>
       <c r="K25">
-        <v>2.514228588629691</v>
+        <v>2.5142285884099005</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00012385428272445416</v>
+        <v>-0.00012385428270217182</v>
       </c>
       <c r="J26">
-        <v>-9.564408482942645e-5</v>
+        <v>-9.564408481505481e-5</v>
       </c>
       <c r="K26">
-        <v>2.3469642808941007</v>
+        <v>2.346964280892627</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.00010006301384960551</v>
+        <v>-0.00010006301385322257</v>
       </c>
       <c r="J27">
-        <v>-7.083148195108531e-5</v>
+        <v>-7.083148195277317e-5</v>
       </c>
       <c r="K27">
-        <v>2.2406142914623532</v>
+        <v>2.24061429165065</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-9.375739605894189e-5</v>
+        <v>-9.37573960668993e-5</v>
       </c>
       <c r="J28">
-        <v>-6.908684948763369e-5</v>
+        <v>-6.908684949351703e-5</v>
       </c>
       <c r="K28">
-        <v>2.248007042335377</v>
+        <v>2.248007042392625</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-8.25699427822589e-5</v>
+        <v>-8.256994280945811e-5</v>
       </c>
       <c r="J29">
-        <v>-6.089171017274093e-5</v>
+        <v>-6.0891710190679936e-5</v>
       </c>
       <c r="K29">
-        <v>2.22107093833567</v>
+        <v>2.2210709384465255</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-8.45377215060161e-5</v>
+        <v>-8.45377215065948e-5</v>
       </c>
       <c r="J30">
-        <v>-6.263263481819135e-5</v>
+        <v>-6.263263481804667e-5</v>
       </c>
       <c r="K30">
-        <v>2.232138689339769</v>
+        <v>2.2321386893865642</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-6.170285318808862e-5</v>
+        <v>-6.17028531687511e-5</v>
       </c>
       <c r="J31">
-        <v>-4.296893337962594e-5</v>
+        <v>-4.296893336863152e-5</v>
       </c>
       <c r="K31">
-        <v>2.1116944127418913</v>
+        <v>2.1116944128495057</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -762,13 +762,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-6.352709715343798e-5</v>
+        <v>-6.352709714413085e-5</v>
       </c>
       <c r="J32">
-        <v>-4.517793683283986e-5</v>
+        <v>-4.517793682758373e-5</v>
       </c>
       <c r="K32">
-        <v>2.138646376440925</v>
+        <v>2.1386463762155334</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_24.xlsx
+++ b/xls/square_12_tri3_24.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>625</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>169</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-0.8548688984298825</v>
+      </c>
+      <c r="J22">
+        <v>-0.7053462782814142</v>
+      </c>
+      <c r="K22">
+        <v>3.59143140489688</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>625</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>-0.5348064050925385</v>
+      </c>
+      <c r="J23">
+        <v>-0.44826753195778096</v>
+      </c>
+      <c r="K23">
+        <v>3.8891688336241272</v>
+      </c>
+    </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>11</v>
